--- a/data/trans_orig/IP07KS_C08_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C08_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de divertirse con sus amigos/as en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de divertirse con sus amigos/as, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7906</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11854</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3385</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9364</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10134</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5671</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8826</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6385</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>38,09%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>866</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2685</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6324</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1625</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121926</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>106557</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>138881</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>81541</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46098</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101766</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>85883</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108859</t>
+          <t>74853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143728</t>
+          <t>95729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>206948</t>
+          <t>207809</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158423</t>
+          <t>189995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234876</t>
+          <t>228482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70745</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56031</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86689</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>74689</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53943</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>111919</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>46,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70004</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86114</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>144693</t>
+          <t>124456</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115740</t>
+          <t>104474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193434</t>
+          <t>142273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11574</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3083</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7084</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1741,102 +1741,102 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5372</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>43575</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37644</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48172</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>29598</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24722</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33560</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>86,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38075</t>
+          <t>25531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47357</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73434</t>
+          <t>74479</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66472</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79298</t>
+          <t>80707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14237</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8481</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4651</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13350</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>17603</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2999</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4661</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>391</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>173407</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>157428</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>190120</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,29%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>117715</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>73170</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>140342</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>177040</t>
+          <t>123774</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158353</t>
+          <t>111427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195529</t>
+          <t>135159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>294755</t>
+          <t>297180</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>239604</t>
+          <t>273982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>320608</t>
+          <t>317365</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>85097</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>69630</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>100837</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>88841</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>66360</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>134984</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>83959</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66763</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>172800</t>
+          <t>154348</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>133760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>232921</t>
+          <t>176391</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>16137</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>7979</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
